--- a/AuditTrail_LIMSv2_output2.xlsx
+++ b/AuditTrail_LIMSv2_output2.xlsx
@@ -191,7 +191,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="19">
+  <fills count="20">
     <fill>
       <patternFill/>
     </fill>
@@ -275,6 +275,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00C0392B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="0027AE60"/>
       </patternFill>
     </fill>
@@ -310,7 +315,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -442,6 +447,9 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1319,7 +1327,7 @@
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>LIMSv2</t>
+          <t>FillV2</t>
         </is>
       </c>
     </row>
@@ -1355,7 +1363,7 @@
       </c>
       <c r="B31" s="10" t="inlineStr">
         <is>
-          <t>2026-04-13 03:28 UTC</t>
+          <t>2026-04-13 04:18 UTC</t>
         </is>
       </c>
     </row>
@@ -1399,7 +1407,7 @@
       </c>
       <c r="B36" s="10" t="inlineStr">
         <is>
-          <t>980  (98.0%)</t>
+          <t>582  (58.2%)</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1490,7 @@
     <row r="47" ht="110" customHeight="1">
       <c r="A47" s="14" t="inlineStr">
         <is>
-          <t>The audit trail for LIMSv2 was reviewed from 01-Apr-2025 to 27-Jun-2025. Of 1,000 recorded events, 20 were escalated for review (20 Critical). Full dataset tier distribution is available in the Full Audit Log sheet.
+          <t>The audit trail for FillV2 was reviewed from 01-Apr-2025 to 27-Jun-2025. Of 1,000 recorded events, 20 were escalated for review (20 Critical). Full dataset tier distribution is available in the Full Audit Log sheet.
 351 instances of missing or inadequate change rationale were identified across the full dataset (not all met the escalation threshold, but the pattern indicates a systemic documentation practice issue).
 A system administrator (dba_prod) directly modified production RESULTS data on record RES-2013, which is inconsistent with Segregation of Duties expectations under 21 CFR Part 11 §11.10(d).
 A chronological impossibility was detected — record RES-2111 shows an approval timestamp before its creation, indicating clock manipulation or direct database alteration.
@@ -1501,7 +1509,7 @@
     <row r="50" ht="72" customHeight="1">
       <c r="A50" s="15" t="inlineStr">
         <is>
-          <t>This audit trail review was performed using rule-based anomaly detection with system-generated narrative summaries. All risk classifications are derived from deterministic rules; narrative text does not influence risk scoring or tier assignment. 1,000 records were reviewed across the period 01-Apr-2025 to 27-Jun-2025. 98.0% of records were automatically cleared as low risk. The 20 records requiring review are documented in the 'Events for Review' sheet. Each finding has been independently reviewed and dispositioned by the undersigned reviewer. The 'System-Proposed Disposition' column is informational only; the reviewer's determination in the 'Reviewer Decision' column reflects independent human judgement and is the authoritative record. Regulatory basis: 21 CFR Part 11 §11.10(e) and EU Annex 11 Clause 9.
+          <t>This audit trail review was performed using rule-based anomaly detection with system-generated narrative summaries. All risk classifications are derived from deterministic rules; narrative text does not influence risk scoring or tier assignment. 1,000 records were reviewed across the period 01-Apr-2025 to 27-Jun-2025. 58.2% of records were automatically cleared as low risk. The 20 records requiring review are documented in the 'Events for Review' sheet. Each finding has been independently reviewed and dispositioned by the undersigned reviewer. The 'System-Proposed Disposition' column is informational only; the reviewer's determination in the 'Reviewer Decision' column reflects independent human judgement and is the authoritative record. Regulatory basis: 21 CFR Part 11 §11.10(e) and EU Annex 11 Clause 9.
 Timezone note: Off-hours scoring (Rule 10) assumes all timestamps in the uploaded file are in the same timezone. If your system exports timestamps in UTC or a non-local timezone, off-hours flags should be interpreted accordingly. Reviewers should verify local shift patterns before dispositing temporal anomalies.</t>
         </is>
       </c>
@@ -55432,7 +55440,7 @@
     <row r="2" ht="14" customHeight="1">
       <c r="A2" s="37" t="inlineStr">
         <is>
-          <t>System: LIMSv2   |   Review Period: 01-Apr-2025 → 27-Jun-2025   |   Generated: 2026-04-13 03:28 UTC</t>
+          <t>System: FillV2   |   Review Period: 01-Apr-2025 → 27-Jun-2025   |   Generated: 2026-04-13 04:18 UTC</t>
         </is>
       </c>
     </row>
@@ -55496,7 +55504,7 @@
       </c>
       <c r="B6" s="43" t="inlineStr">
         <is>
-          <t>NO — No Findings</t>
+          <t>YES — Findings Present</t>
         </is>
       </c>
       <c r="C6" s="42" t="inlineStr">
@@ -55507,7 +55515,7 @@
       </c>
       <c r="D6" s="42" t="inlineStr">
         <is>
-          <t>No deletion or data loss patterns detected in the reviewed period.</t>
+          <t>Rule 6 (Record Reconstruction) and/or Rule 7 (Sensitive Deletion) findings detected. See Events for Review sheet for specific records and recommended actions.</t>
         </is>
       </c>
     </row>
@@ -55517,7 +55525,7 @@
           <t>3. Is the audit trail protected from unauthorised modification?</t>
         </is>
       </c>
-      <c r="B7" s="43" t="inlineStr">
+      <c r="B7" s="44" t="inlineStr">
         <is>
           <t>NO FINDINGS</t>
         </is>
@@ -55540,7 +55548,7 @@
           <t>4. Does the audit trail show unauthorised access attempts?</t>
         </is>
       </c>
-      <c r="B8" s="43" t="inlineStr">
+      <c r="B8" s="44" t="inlineStr">
         <is>
           <t>NO — No Findings</t>
         </is>
@@ -55563,7 +55571,7 @@
           <t>5. Have unauthorised system configuration changes occurred (incl. date/time)?</t>
         </is>
       </c>
-      <c r="B9" s="43" t="inlineStr">
+      <c r="B9" s="44" t="inlineStr">
         <is>
           <t>NO FINDINGS</t>
         </is>
@@ -55609,7 +55617,7 @@
           <t>7. Are generic, shared, and service accounts appropriately controlled?</t>
         </is>
       </c>
-      <c r="B11" s="44" t="inlineStr">
+      <c r="B11" s="45" t="inlineStr">
         <is>
           <t>CONCERN — Rule 12/13 Findings</t>
         </is>
@@ -55634,22 +55642,22 @@
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="45" t="inlineStr">
+      <c r="A14" s="46" t="inlineStr">
         <is>
           <t>Reviewer Name:</t>
         </is>
       </c>
-      <c r="B14" s="45" t="inlineStr">
+      <c r="B14" s="46" t="inlineStr">
         <is>
           <t>Signature:</t>
         </is>
       </c>
-      <c r="C14" s="45" t="inlineStr">
+      <c r="C14" s="46" t="inlineStr">
         <is>
           <t>Date:</t>
         </is>
       </c>
-      <c r="D14" s="45" t="inlineStr">
+      <c r="D14" s="46" t="inlineStr">
         <is>
           <t>Title / Role:</t>
         </is>
